--- a/artfynd/A 35641-2025 artfynd.xlsx
+++ b/artfynd/A 35641-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82532819</v>
+        <v>82532817</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roparnäset, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514617.4688115417</v>
+        <v>514466</v>
       </c>
       <c r="R2" t="n">
-        <v>7286026.42852555</v>
+        <v>7285963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +743,9 @@
           <t>2020-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +762,26 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Färsk granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Färsk granlåga</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -794,6 +794,342 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>82532814</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Roparnäset, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514466</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7285963</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Färsk granlåga</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Färsk granlåga</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>82532818</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Roparnäset, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>514466</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7285963</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>82532819</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Roparnäset, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>514617</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7286026</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Tärna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-03-01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
